--- a/Dati/PDV-e-ESATTORI.xlsx
+++ b/Dati/PDV-e-ESATTORI.xlsx
@@ -1,42 +1,1446 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{DAC535C9-1D18-0F48-B6A5-D04121F70256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="463">
+  <si>
+    <t>CODICE SEDE</t>
+  </si>
+  <si>
+    <t>DENOMINAZIONE ESERCENTE</t>
+  </si>
+  <si>
+    <t>INDIRIZZO</t>
+  </si>
+  <si>
+    <t>COMUNE</t>
+  </si>
+  <si>
+    <t>PROVINCIA</t>
+  </si>
+  <si>
+    <t>MQ</t>
+  </si>
+  <si>
+    <t>N° PDA</t>
+  </si>
+  <si>
+    <t>N° AWP</t>
+  </si>
+  <si>
+    <t>CIM69484</t>
+  </si>
+  <si>
+    <t>CHIARA E STEFY SRL</t>
+  </si>
+  <si>
+    <t>BAR SABRINA</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA 44</t>
+  </si>
+  <si>
+    <t>CAMPOROSSO</t>
+  </si>
+  <si>
+    <t>IMPERIA</t>
+  </si>
+  <si>
+    <t>CIM69486</t>
+  </si>
+  <si>
+    <t>GREENS' BAR CAFFETECA DI SCORDO SANDRA</t>
+  </si>
+  <si>
+    <t>GREEN 'S BAR  CAFFETECA</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA 96</t>
+  </si>
+  <si>
+    <t>BORDIGHERA</t>
+  </si>
+  <si>
+    <t>CIM69541</t>
+  </si>
+  <si>
+    <t>BAR ARISTON DI AGNOGNE SILVIO E ROLANDO ELVIRA SNC</t>
+  </si>
+  <si>
+    <t>BAR ARISTON</t>
+  </si>
+  <si>
+    <t>VIA PIAZZA DELLA STAZIONE 1</t>
+  </si>
+  <si>
+    <t>TAGGIA</t>
+  </si>
+  <si>
+    <t>CIM40510</t>
+  </si>
+  <si>
+    <t>OLIMPIA DI TRIGNANI FLAVIO</t>
+  </si>
+  <si>
+    <t>BAR OLIMPIA</t>
+  </si>
+  <si>
+    <t>VIA GROSSI BIANCHI 58</t>
+  </si>
+  <si>
+    <t>SAN REMO</t>
+  </si>
+  <si>
+    <t>CIM69443</t>
+  </si>
+  <si>
+    <t>CALCAGNO SILVIA</t>
+  </si>
+  <si>
+    <t>TABACCHI CALCAGNO SILVIA</t>
+  </si>
+  <si>
+    <t>VIA GALILEO GALILEI 177</t>
+  </si>
+  <si>
+    <t>SANREMO</t>
+  </si>
+  <si>
+    <t>CIM70520</t>
+  </si>
+  <si>
+    <t>VENEZIANO NICOLA</t>
+  </si>
+  <si>
+    <t>BAR FIORUCCI</t>
+  </si>
+  <si>
+    <t>VIA VITTORIO VENETO 21/C</t>
+  </si>
+  <si>
+    <t>VENTIMIGLIA</t>
+  </si>
+  <si>
+    <t>CIM69572</t>
+  </si>
+  <si>
+    <t>BAR SPORT DI AMIANTO TATIANA</t>
+  </si>
+  <si>
+    <t>BAR SPORT</t>
+  </si>
+  <si>
+    <t>VIA BLENGINO 37</t>
+  </si>
+  <si>
+    <t>CSV69524</t>
+  </si>
+  <si>
+    <t>MONTELEONE MARISA</t>
+  </si>
+  <si>
+    <t>TABACCHERIA N. 13 DI MONTELEONE MARISA</t>
+  </si>
+  <si>
+    <t>VIA VIA PIAVE 71</t>
+  </si>
+  <si>
+    <t>ALBENGA</t>
+  </si>
+  <si>
+    <t>SAVONA</t>
+  </si>
+  <si>
+    <t>CIM69756</t>
+  </si>
+  <si>
+    <t>BAR BRISTOL DI SPANO' FRANCESCO</t>
+  </si>
+  <si>
+    <t>BAR BRISTOL</t>
+  </si>
+  <si>
+    <t>CORSO LIMONE PIEMONTE 43</t>
+  </si>
+  <si>
+    <t>CIM69481</t>
+  </si>
+  <si>
+    <t>SIGNORI MASSIMO</t>
+  </si>
+  <si>
+    <t>TABACCHI N. 56</t>
+  </si>
+  <si>
+    <t>VIA VIA GOETHE 88</t>
+  </si>
+  <si>
+    <t>CIM45372</t>
+  </si>
+  <si>
+    <t>GARIBALDI NATALE</t>
+  </si>
+  <si>
+    <t>TABACCHERIA GARIBALDI NATALE</t>
+  </si>
+  <si>
+    <t>VIA G. MATTEOTTI 179</t>
+  </si>
+  <si>
+    <t>CSV69512</t>
+  </si>
+  <si>
+    <t>SANGIORGIO GEST. SRL</t>
+  </si>
+  <si>
+    <t>BUFFET STAZIONE VARAZZE</t>
+  </si>
+  <si>
+    <t>VIA VIA SANT'AMBROGIO 20</t>
+  </si>
+  <si>
+    <t>VARAZZE</t>
+  </si>
+  <si>
+    <t>CIM68507</t>
+  </si>
+  <si>
+    <t>SNACK BAR 84 DI GANGALE ALESSIA E C. S.A .S.</t>
+  </si>
+  <si>
+    <t>SNACK BAR 84</t>
+  </si>
+  <si>
+    <t>VIA VIA STAZIONE 205</t>
+  </si>
+  <si>
+    <t>CIM69483</t>
+  </si>
+  <si>
+    <t>CONTE SARA</t>
+  </si>
+  <si>
+    <t>BLU  BAR</t>
+  </si>
+  <si>
+    <t>VIA VIA COL. APROSIO 268</t>
+  </si>
+  <si>
+    <t>VALLECROSIA</t>
+  </si>
+  <si>
+    <t>CIM69592</t>
+  </si>
+  <si>
+    <t>STELLA D'ITALIA S.N.C. DI CRISTIANO CRES PI &amp; C.</t>
+  </si>
+  <si>
+    <t>STAR PUB</t>
+  </si>
+  <si>
+    <t>CORSO ITALIA 113/B</t>
+  </si>
+  <si>
+    <t>CERIANA</t>
+  </si>
+  <si>
+    <t>CIM69579</t>
+  </si>
+  <si>
+    <t>GAGLIANO ANTONIO &amp; C. S.A.S.</t>
+  </si>
+  <si>
+    <t>BAR NIKI DI GAGLIANO ANTONIO E C SAS</t>
+  </si>
+  <si>
+    <t>VIA VIA CASCIONE 88</t>
+  </si>
+  <si>
+    <t>CIM69747</t>
+  </si>
+  <si>
+    <t>NINA SNC DI SANAPO</t>
+  </si>
+  <si>
+    <t>BAR ALAIN</t>
+  </si>
+  <si>
+    <t>VIA DANTE ALIGHIERI 304</t>
+  </si>
+  <si>
+    <t>CIM68489</t>
+  </si>
+  <si>
+    <t>AGUIRRE JULIA ALICIA</t>
+  </si>
+  <si>
+    <t>RIVENDITA TABACCHI EDICOLA AGUIRRE JULIA ALICIA</t>
+  </si>
+  <si>
+    <t>VIA BRAIE 295</t>
+  </si>
+  <si>
+    <t>CIM69480</t>
+  </si>
+  <si>
+    <t>BAR TRIESTE DI CIUFFODORO CLAUDIO</t>
+  </si>
+  <si>
+    <t>BAR TRIESTE</t>
+  </si>
+  <si>
+    <t>VIA VIA DANTE ALIGHIERI 4</t>
+  </si>
+  <si>
+    <t>CIM68485</t>
+  </si>
+  <si>
+    <t>BONUOMO INES</t>
+  </si>
+  <si>
+    <t>BAR FRONTIERA</t>
+  </si>
+  <si>
+    <t>STRADA STATALE 20</t>
+  </si>
+  <si>
+    <t>CSV69444</t>
+  </si>
+  <si>
+    <t>COLOMBO GIOVANNA</t>
+  </si>
+  <si>
+    <t>LA CAFFETTERIA</t>
+  </si>
+  <si>
+    <t>CORSO TARDY E BENECH 71/73</t>
+  </si>
+  <si>
+    <t>CIM68495</t>
+  </si>
+  <si>
+    <t>CATULLO STEFANO</t>
+  </si>
+  <si>
+    <t>BAR DIANA</t>
+  </si>
+  <si>
+    <t>VIA APROSIO 462</t>
+  </si>
+  <si>
+    <t>CIM31466</t>
+  </si>
+  <si>
+    <t>CAVALIERE DENIS</t>
+  </si>
+  <si>
+    <t>BAR ELENA DI CAVALIERE DENIS</t>
+  </si>
+  <si>
+    <t>VIA PROVINCIALE 29</t>
+  </si>
+  <si>
+    <t>SAN BIAGIO DELLA CIMA</t>
+  </si>
+  <si>
+    <t>CIM68483</t>
+  </si>
+  <si>
+    <t>CARLO MAURO</t>
+  </si>
+  <si>
+    <t>TABACCHI CARLO MAURO</t>
+  </si>
+  <si>
+    <t>VIA VITTORIO EMANUELE 489</t>
+  </si>
+  <si>
+    <t>CSV68508</t>
+  </si>
+  <si>
+    <t>B.C. SNC DI BERTINI A., CASSAI P. &amp; C.</t>
+  </si>
+  <si>
+    <t>BAR DELL'AUTOSTRADA</t>
+  </si>
+  <si>
+    <t>CORSO SVIZZERA 50/R</t>
+  </si>
+  <si>
+    <t>CSV69578</t>
+  </si>
+  <si>
+    <t>BAR LE SERRE</t>
+  </si>
+  <si>
+    <t>REGIONE BAGNOLI 37</t>
+  </si>
+  <si>
+    <t>CIM47887</t>
+  </si>
+  <si>
+    <t>B.M. SNC DI BERNARDINI MAURO E MARTINI ELISA</t>
+  </si>
+  <si>
+    <t>BAR LADY</t>
+  </si>
+  <si>
+    <t>VIA DIANO CALDERINA 2</t>
+  </si>
+  <si>
+    <t>DIANO MARINA</t>
+  </si>
+  <si>
+    <t>CIM69590</t>
+  </si>
+  <si>
+    <t>CALDERINI MIRKO &amp; C. S.A.S.</t>
+  </si>
+  <si>
+    <t>CAFFE' DEL CORSO</t>
+  </si>
+  <si>
+    <t>VIA VIA NINO BIXIO 13</t>
+  </si>
+  <si>
+    <t>RIVA LIGURE</t>
+  </si>
+  <si>
+    <t>CIM68515</t>
+  </si>
+  <si>
+    <t>CANAVESIO ALDO &amp; C. SOCIETA' IN ACCOMAND ITA SEMPLICE</t>
+  </si>
+  <si>
+    <t>BAR CHARLIE 4</t>
+  </si>
+  <si>
+    <t>VIA GENERALE ARDOINO 1</t>
+  </si>
+  <si>
+    <t>CIM69503</t>
+  </si>
+  <si>
+    <t>BAR LATTERIA DI RUBAUDO ANNA MARIA &amp; C S AS</t>
+  </si>
+  <si>
+    <t>BAR LATTERIA REBAUDO</t>
+  </si>
+  <si>
+    <t>VIA VIA GARESSIO 12</t>
+  </si>
+  <si>
+    <t>CIM68499</t>
+  </si>
+  <si>
+    <t>GRISERI ROCCO</t>
+  </si>
+  <si>
+    <t>RIVENDITA TABACCHI N.11 GRISERI</t>
+  </si>
+  <si>
+    <t>VIA STAZIONE 133</t>
+  </si>
+  <si>
+    <t>CIM68498</t>
+  </si>
+  <si>
+    <t>BAR CARAVELLA SNC DI FIORONE &amp; C.</t>
+  </si>
+  <si>
+    <t>BAR CARAVELLE</t>
+  </si>
+  <si>
+    <t>PIAZZA SAFFI 20</t>
+  </si>
+  <si>
+    <t>SANTO STEFANO AL MARE</t>
+  </si>
+  <si>
+    <t>CIM69448</t>
+  </si>
+  <si>
+    <t>FEDO SNC DI BIAGINI EDOARDO E C SNC</t>
+  </si>
+  <si>
+    <t>IL BARETTO</t>
+  </si>
+  <si>
+    <t>VIA LUNGOMARE D'ALBERTIS 39</t>
+  </si>
+  <si>
+    <t>CIM69604</t>
+  </si>
+  <si>
+    <t>REVELLO DAVIDE</t>
+  </si>
+  <si>
+    <t>RIVENDITA REVELLO DAVIDE</t>
+  </si>
+  <si>
+    <t>VIA IV NOVEMBRE 29</t>
+  </si>
+  <si>
+    <t>CIM69454</t>
+  </si>
+  <si>
+    <t>SORVILLO ENRICO</t>
+  </si>
+  <si>
+    <t>BAR TABACCHI  AZZURRO</t>
+  </si>
+  <si>
+    <t>VIA TENDA 24</t>
+  </si>
+  <si>
+    <t>CIM68490</t>
+  </si>
+  <si>
+    <t>BAR SERENELLA SNC DI DELLA CROCE BRUNO E  ANNA</t>
+  </si>
+  <si>
+    <t>BAR SERENELLA</t>
+  </si>
+  <si>
+    <t>CORSO MAZZINI 599</t>
+  </si>
+  <si>
+    <t>CIM69575</t>
+  </si>
+  <si>
+    <t>F.LLI LANTERI SAS</t>
+  </si>
+  <si>
+    <t>BAR  ASTRA</t>
+  </si>
+  <si>
+    <t>VIA BOSELLI 44</t>
+  </si>
+  <si>
+    <t>CSV54757</t>
+  </si>
+  <si>
+    <t>PROSTAMO CONCETTA</t>
+  </si>
+  <si>
+    <t>TABACCHINO N.4 PROSTAMO CONCETTA</t>
+  </si>
+  <si>
+    <t>VIALE LIGURIA 10/R</t>
+  </si>
+  <si>
+    <t>ALBISSOLA MARINA</t>
+  </si>
+  <si>
+    <t>CSV69546</t>
+  </si>
+  <si>
+    <t>FALCONERI DI BORJA MORAN YADIRA PILAR</t>
+  </si>
+  <si>
+    <t>BAR IL PARADISO DEL CAFFE'</t>
+  </si>
+  <si>
+    <t>PIAZZA MARCONI 3</t>
+  </si>
+  <si>
+    <t>PIETRA LIGURE</t>
+  </si>
+  <si>
+    <t>CIM69674</t>
+  </si>
+  <si>
+    <t>BAR ORCHIDEA DI FERRARI UGO E MONICA S.N .C.</t>
+  </si>
+  <si>
+    <t>BAR ORCHIDEA</t>
+  </si>
+  <si>
+    <t>VIA LIBERTA 36</t>
+  </si>
+  <si>
+    <t>CIM69457</t>
+  </si>
+  <si>
+    <t>TOGNINI ERICA</t>
+  </si>
+  <si>
+    <t>BAR RISTORO AGLI ORTI</t>
+  </si>
+  <si>
+    <t>VIA LUNGO ARGINE DESTRO REGIONE ANGUILLE SNC</t>
+  </si>
+  <si>
+    <t>CIM69602</t>
+  </si>
+  <si>
+    <t>PAVESI SERGIO EMILIO</t>
+  </si>
+  <si>
+    <t>RIVENDITA TABACCHI NÂ° 3 PAVESI</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA 116</t>
+  </si>
+  <si>
+    <t>CIM69442</t>
+  </si>
+  <si>
+    <t>BACCARA' SAS DI CAFFAGNI CRISTIAN &amp; C</t>
+  </si>
+  <si>
+    <t>BAR BUNNY 2</t>
+  </si>
+  <si>
+    <t>VIA MARTIRI 344</t>
+  </si>
+  <si>
+    <t>CIM69738</t>
+  </si>
+  <si>
+    <t>ASCOT CLUB A.S.D.</t>
+  </si>
+  <si>
+    <t>ASCOT CLUB ASD</t>
+  </si>
+  <si>
+    <t>VIA COL. APROSIO 225</t>
+  </si>
+  <si>
+    <t>CIM69440</t>
+  </si>
+  <si>
+    <t>SMAGUR ELZBIETA</t>
+  </si>
+  <si>
+    <t>BAR DA ELA</t>
+  </si>
+  <si>
+    <t>VIA C.SO CAVALLOTTI 166</t>
+  </si>
+  <si>
+    <t>CIM56899</t>
+  </si>
+  <si>
+    <t>REAL DREAM SAS DI LUCA' SEBASTIANO</t>
+  </si>
+  <si>
+    <t>SALA GIOCHI REAL DREAM</t>
+  </si>
+  <si>
+    <t>VIA NINO BIXIO 21</t>
+  </si>
+  <si>
+    <t>CIM68529</t>
+  </si>
+  <si>
+    <t>SAI.BER. DI CASSAI P. &amp; BERTINI A. S.N.C .</t>
+  </si>
+  <si>
+    <t>BAR DEL CENTRO</t>
+  </si>
+  <si>
+    <t>VIA NAZIONALE 1</t>
+  </si>
+  <si>
+    <t>PONTEDASSIO</t>
+  </si>
+  <si>
+    <t>CIM69565</t>
+  </si>
+  <si>
+    <t>GIORDIE SNC DI BENATTI ROBERTA E BENATTI  DIEGO</t>
+  </si>
+  <si>
+    <t>BAR GIORDIE</t>
+  </si>
+  <si>
+    <t>VIA COLLONELLO APROSIO 193</t>
+  </si>
+  <si>
+    <t>CIM68482</t>
+  </si>
+  <si>
+    <t>REINERO RUGGERO</t>
+  </si>
+  <si>
+    <t>RIVENDITA TABACCHI CALCIO BAR</t>
+  </si>
+  <si>
+    <t>CORSO MAZZINI 18</t>
+  </si>
+  <si>
+    <t>CIM69555</t>
+  </si>
+  <si>
+    <t>ROVERE LUCA</t>
+  </si>
+  <si>
+    <t>TABACCHERIA ROVERE</t>
+  </si>
+  <si>
+    <t>VIA VIA GALILEO GALILEI 2</t>
+  </si>
+  <si>
+    <t>CIM69603</t>
+  </si>
+  <si>
+    <t>FICHERA MANUEL</t>
+  </si>
+  <si>
+    <t>TABACCHERIA PANTAN</t>
+  </si>
+  <si>
+    <t>VIA VIA SOLERI 14</t>
+  </si>
+  <si>
+    <t>CIM69544</t>
+  </si>
+  <si>
+    <t>MOLLAALIU FLORIAN</t>
+  </si>
+  <si>
+    <t>BAR SEVEN</t>
+  </si>
+  <si>
+    <t>VIA LUNGOMARE C.COLOMBO 146</t>
+  </si>
+  <si>
+    <t>CIM69543</t>
+  </si>
+  <si>
+    <t>RUBICONE EROS</t>
+  </si>
+  <si>
+    <t>TABACCHERIA NÂ° 1</t>
+  </si>
+  <si>
+    <t>VIA GENOVA 2/4</t>
+  </si>
+  <si>
+    <t>CSV69513</t>
+  </si>
+  <si>
+    <t>BAR FORTINI DI RUSSO G. &amp; C. SAS</t>
+  </si>
+  <si>
+    <t>BAR FORTINI DI RUSSO G.&amp;C. S.A.S</t>
+  </si>
+  <si>
+    <t>VIA REGIONE ANTOGNANO 57</t>
+  </si>
+  <si>
+    <t>CIM68565</t>
+  </si>
+  <si>
+    <t>BRESCIA FRANCESCA</t>
+  </si>
+  <si>
+    <t>BAR TUCANO</t>
+  </si>
+  <si>
+    <t>CORSO CAVALLOTTI 141</t>
+  </si>
+  <si>
+    <t>CIM68509</t>
+  </si>
+  <si>
+    <t>BAR MONDOVI' SNC</t>
+  </si>
+  <si>
+    <t>BAR MONDOVI'</t>
+  </si>
+  <si>
+    <t>PIAZZA SAN SEBASTIANO 5</t>
+  </si>
+  <si>
+    <t>CIM68491</t>
+  </si>
+  <si>
+    <t>GANDOLFO KATIA</t>
+  </si>
+  <si>
+    <t>RIV. TABACCHI DI GANDOLFO KATIA</t>
+  </si>
+  <si>
+    <t>VIA LITTARDI 188</t>
+  </si>
+  <si>
+    <t>CSV69514</t>
+  </si>
+  <si>
+    <t>MB S.N.C. DI SIVIERO DAVIDE E MASSIMO</t>
+  </si>
+  <si>
+    <t>MOKA BAR</t>
+  </si>
+  <si>
+    <t>VIA CORSO DANTE ANGOLO VIA DIAZ 15</t>
+  </si>
+  <si>
+    <t>ALASSIO</t>
+  </si>
+  <si>
+    <t>CSV69549</t>
+  </si>
+  <si>
+    <t>IACHINI ROBERTO</t>
+  </si>
+  <si>
+    <t>BAR CIANIN CIANIN</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA 130</t>
+  </si>
+  <si>
+    <t>LOANO</t>
+  </si>
+  <si>
+    <t>CSV69556</t>
+  </si>
+  <si>
+    <t>RIV. TABACCHI N.10 IACHINI ROBERTO</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA 132</t>
+  </si>
+  <si>
+    <t>CSV69550</t>
+  </si>
+  <si>
+    <t>ZARRILLO ANTONIO</t>
+  </si>
+  <si>
+    <t>NEW BARETTO</t>
+  </si>
+  <si>
+    <t>VIA P.ZZA FRANCHELLI 2</t>
+  </si>
+  <si>
+    <t>CIM69563</t>
+  </si>
+  <si>
+    <t>POGGI YURI</t>
+  </si>
+  <si>
+    <t>RIVENDITA N. 21 POGGI YURI</t>
+  </si>
+  <si>
+    <t>VIA VIA MARSAGLIA 61</t>
+  </si>
+  <si>
+    <t>CSV69441</t>
+  </si>
+  <si>
+    <t>BAR TABOGA DI ORSOLINI RENATO</t>
+  </si>
+  <si>
+    <t>BAR TABOGA</t>
+  </si>
+  <si>
+    <t>VIA DEI GAZZI 71</t>
+  </si>
+  <si>
+    <t>CSV69455</t>
+  </si>
+  <si>
+    <t>RUOCCO MIRCO</t>
+  </si>
+  <si>
+    <t>TABACCHI EUROPA RIVENDITA N. 10</t>
+  </si>
+  <si>
+    <t>CORSO EUROPA 55</t>
+  </si>
+  <si>
+    <t>CIM69618</t>
+  </si>
+  <si>
+    <t>C. &amp; C. GROUP SRL</t>
+  </si>
+  <si>
+    <t>C E C GROUP SRL</t>
+  </si>
+  <si>
+    <t>VIA STAZIONE 125</t>
+  </si>
+  <si>
+    <t>CIM69438</t>
+  </si>
+  <si>
+    <t>PAVANI E PEANO SNC</t>
+  </si>
+  <si>
+    <t>PICCOLO BAR</t>
+  </si>
+  <si>
+    <t>VIA VIA XX SETTEMBRE 35</t>
+  </si>
+  <si>
+    <t>OSPEDALETTI</t>
+  </si>
+  <si>
+    <t>CIM67176</t>
+  </si>
+  <si>
+    <t>BAR CALYPSO DI CASCIO ROBERTO</t>
+  </si>
+  <si>
+    <t>BAR CALYPSO</t>
+  </si>
+  <si>
+    <t>VIA VITTORIO EMANUELE 284</t>
+  </si>
+  <si>
+    <t>CIM59021</t>
+  </si>
+  <si>
+    <t>LA ROCCA FABRIZIO</t>
+  </si>
+  <si>
+    <t>LA ROCCA FABRIZIO IL TABACCAIO 2.0</t>
+  </si>
+  <si>
+    <t>VIA VITTORIO EMANUELE II 387</t>
+  </si>
+  <si>
+    <t>CIM69605</t>
+  </si>
+  <si>
+    <t>VALENTINI FOOD SRLS</t>
+  </si>
+  <si>
+    <t>CAFFE' DEL DUOMO</t>
+  </si>
+  <si>
+    <t>VIA STRAFFORELLO 6</t>
+  </si>
+  <si>
+    <t>CIM69395</t>
+  </si>
+  <si>
+    <t>ICE ON FIRE DI SALIHI SAIMIR</t>
+  </si>
+  <si>
+    <t>BAR ICE ON FIRE</t>
+  </si>
+  <si>
+    <t>VIA RAMBALDO 42</t>
+  </si>
+  <si>
+    <t>CIM69571</t>
+  </si>
+  <si>
+    <t>GUTTI SNC DI GULLACE FEDERICA &amp; C.</t>
+  </si>
+  <si>
+    <t>CAFFE' DELLE HARPAE</t>
+  </si>
+  <si>
+    <t>PIAZZA MARTIRI 24</t>
+  </si>
+  <si>
+    <t>ISOLABONA</t>
+  </si>
+  <si>
+    <t>CIM68502</t>
+  </si>
+  <si>
+    <t>R.E.M. S.N.C. DI ELENA RITA &amp; C.</t>
+  </si>
+  <si>
+    <t>STAZIONE DI SERVIZIO TAMOIL DI R.E.M. S.N.C.</t>
+  </si>
+  <si>
+    <t>VIA LITTARDI 56</t>
+  </si>
+  <si>
+    <t>CIM68511</t>
+  </si>
+  <si>
+    <t>LANTERI CRAVET FRANCA</t>
+  </si>
+  <si>
+    <t>TABACCHERIA RIVENDITA N 1 LANTERI CRAVET</t>
+  </si>
+  <si>
+    <t>VIA ROMA 108</t>
+  </si>
+  <si>
+    <t>SAN BARTOLOMEO AL MARE</t>
+  </si>
+  <si>
+    <t>CIM68516</t>
+  </si>
+  <si>
+    <t>COZZITORTO SIMONE</t>
+  </si>
+  <si>
+    <t>TABACCHERIA RIV. N. 3 DI COZZITORTO SIMONE</t>
+  </si>
+  <si>
+    <t>VIA BOSELLI 18</t>
+  </si>
+  <si>
+    <t>CIM69744</t>
+  </si>
+  <si>
+    <t>GUIDA GIUSEPPE ELIANO</t>
+  </si>
+  <si>
+    <t>BAR RISTORANTE NICO</t>
+  </si>
+  <si>
+    <t>VIA AMICIS 9</t>
+  </si>
+  <si>
+    <t>CIM69796</t>
+  </si>
+  <si>
+    <t>BAR GALEONE S.A.S. DI CIRIBILLI FEDERICA  &amp; C.</t>
+  </si>
+  <si>
+    <t>BAR GALEONE</t>
+  </si>
+  <si>
+    <t>VIA DANTE 22</t>
+  </si>
+  <si>
+    <t>CIM69673</t>
+  </si>
+  <si>
+    <t>RICCA ALESSANDRO</t>
+  </si>
+  <si>
+    <t>TABACCHI RICCA ALESSANDRO</t>
+  </si>
+  <si>
+    <t>VIA QUEIROLO 100</t>
+  </si>
+  <si>
+    <t>CIM69818</t>
+  </si>
+  <si>
+    <t>CAFE' NENA DI ARSI' MILENA</t>
+  </si>
+  <si>
+    <t>BAR NENA</t>
+  </si>
+  <si>
+    <t>VIA GIUSEPPE GARIBALDI 9/A</t>
+  </si>
+  <si>
+    <t>CSV69824</t>
+  </si>
+  <si>
+    <t>CASSATA DOMENICO</t>
+  </si>
+  <si>
+    <t>RIVENDITA TAB. N. 9 DI CASSATA DOMENICO</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA 295</t>
+  </si>
+  <si>
+    <t>CSV69716</t>
+  </si>
+  <si>
+    <t>ZHANG RENYI</t>
+  </si>
+  <si>
+    <t>TIPOTA CAFFE'</t>
+  </si>
+  <si>
+    <t>CORSO EUROPA 12/14</t>
+  </si>
+  <si>
+    <t>BORGHETTO SANTO SPIRITO</t>
+  </si>
+  <si>
+    <t>CIM32055</t>
+  </si>
+  <si>
+    <t>LUCI SORRENTINO MARIAERSILIA</t>
+  </si>
+  <si>
+    <t>BAR CUVENTU</t>
+  </si>
+  <si>
+    <t>VIA CHIAPPORI 20/A</t>
+  </si>
+  <si>
+    <t>CIM69739</t>
+  </si>
+  <si>
+    <t>ASSOCIAZIONE SPORTIVA BILIARDO 2 A MO' D I 3 A.S.D.</t>
+  </si>
+  <si>
+    <t>BILIARDO CLUB 2 A MO' DI 3 A.S.D.</t>
+  </si>
+  <si>
+    <t>VIA AURELIA 92</t>
+  </si>
+  <si>
+    <t>CIM69564</t>
+  </si>
+  <si>
+    <t>TABACCHERIA ANNA E FRANCESCO DI FRANCESC O ESPOSITO</t>
+  </si>
+  <si>
+    <t>TABACCHERIA ANNA E FRANCESCO DI FRANCESCO ESPOSITO</t>
+  </si>
+  <si>
+    <t>VIA VIA AURELIA LEVANTE 37</t>
+  </si>
+  <si>
+    <t>CIM69485</t>
+  </si>
+  <si>
+    <t>BAR POIANA DI POIANA NATALIA</t>
+  </si>
+  <si>
+    <t>BAR POIANA</t>
+  </si>
+  <si>
+    <t>VIA P.ZZA D'ARMI 30</t>
+  </si>
+  <si>
+    <t>CIM70593</t>
+  </si>
+  <si>
+    <t>BAR LAMARMORA DI SAMBERO MARIA FRANCESCA</t>
+  </si>
+  <si>
+    <t>BAR LAMARMORA</t>
+  </si>
+  <si>
+    <t>VIA LAMARMORA 249</t>
+  </si>
+  <si>
+    <t>CIM70128</t>
+  </si>
+  <si>
+    <t>MAX'S CAFE' DI LUNETTO MASSIMO</t>
+  </si>
+  <si>
+    <t>MAX'S CAFE</t>
+  </si>
+  <si>
+    <t>CORSO DELLA REPUBBLICA 36</t>
+  </si>
+  <si>
+    <t>CIM70502</t>
+  </si>
+  <si>
+    <t>BAR TABACCHI LA FONTANA</t>
+  </si>
+  <si>
+    <t>PIAZZA FONTANA 2</t>
+  </si>
+  <si>
+    <t>CSV69586</t>
+  </si>
+  <si>
+    <t>ESPOSITO CATELLO MATTEO</t>
+  </si>
+  <si>
+    <t>VELVET BAR</t>
+  </si>
+  <si>
+    <t>CORSO EUROPA 19</t>
+  </si>
+  <si>
+    <t>CIM69643</t>
+  </si>
+  <si>
+    <t>BAR GALILEI DI PELLEGRINI ANDREA</t>
+  </si>
+  <si>
+    <t>BAR  GALILEI</t>
+  </si>
+  <si>
+    <t>VIA GALILEO GALILEI 569</t>
+  </si>
+  <si>
+    <t>CIM70219</t>
+  </si>
+  <si>
+    <t>BORGESE DAVID</t>
+  </si>
+  <si>
+    <t>TABACCHERIA RIV.1 BORGESE DAVID</t>
+  </si>
+  <si>
+    <t>VIA C.  COLOMBO 22</t>
+  </si>
+  <si>
+    <t>BADALUCCO</t>
+  </si>
+  <si>
+    <t>CIM69536</t>
+  </si>
+  <si>
+    <t>BIANCHERI SABRINA</t>
+  </si>
+  <si>
+    <t>KAOS CAFFE'</t>
+  </si>
+  <si>
+    <t>VIA VITTORIO EMANUELE 229</t>
+  </si>
+  <si>
+    <t>CIM69761</t>
+  </si>
+  <si>
+    <t>AL PICCOLO RITROVO DI COPPOLA DANIELA</t>
+  </si>
+  <si>
+    <t>BAR AL PICCOLO RITROVO</t>
+  </si>
+  <si>
+    <t>VIA PIETRO AGOSTI 122</t>
+  </si>
+  <si>
+    <t>CIM69488</t>
+  </si>
+  <si>
+    <t>ZUCCHIATTI FIORELLA PIERINA</t>
+  </si>
+  <si>
+    <t>BAR EMILIO</t>
+  </si>
+  <si>
+    <t>PIAZZA EROI TAGGESI 2</t>
+  </si>
+  <si>
+    <t>CIM68500</t>
+  </si>
+  <si>
+    <t>PULCINELLA TABACCHI DI CORREALE FRANCESC A</t>
+  </si>
+  <si>
+    <t>TABACCHI PULCINELLA</t>
+  </si>
+  <si>
+    <t>VIA AURELIA PONENTE 202</t>
+  </si>
+  <si>
+    <t>CIM68501</t>
+  </si>
+  <si>
+    <t>LELA FATJON</t>
+  </si>
+  <si>
+    <t>BAR TEATRO DI LALA FATJON</t>
+  </si>
+  <si>
+    <t>VIA VIGNASSE 5</t>
+  </si>
+  <si>
+    <t>SAN LORENZO AL MARE</t>
+  </si>
+  <si>
+    <t>CIM70649</t>
+  </si>
+  <si>
+    <t>QUATTRONE ROMANO</t>
+  </si>
+  <si>
+    <t>RIV. TABACCHI QUATTRONE ROMANO</t>
+  </si>
+  <si>
+    <t>VIA MARTIRI DELLA LIBERTÀ 39</t>
+  </si>
+  <si>
+    <t>CIM71242</t>
+  </si>
+  <si>
+    <t>MASUERO CRISTIANO</t>
+  </si>
+  <si>
+    <t>VIA VIA LUDOVICO BREA 37/39</t>
+  </si>
+  <si>
+    <t>CIM68487</t>
+  </si>
+  <si>
+    <t>BALLESTRA AGNESE</t>
+  </si>
+  <si>
+    <t>TABACCHERIA BALLESTRA AGNESE</t>
+  </si>
+  <si>
+    <t>VIA APROSIO 176</t>
+  </si>
+  <si>
+    <t>CIM71097</t>
+  </si>
+  <si>
+    <t>GIRO PIZZA DI LACI RIGERS</t>
+  </si>
+  <si>
+    <t>LA DOLCEVITA BAR PIZZERIA</t>
+  </si>
+  <si>
+    <t>PIAZZA GARIBALDI 2</t>
+  </si>
+  <si>
+    <t>DOLCEACQUA</t>
+  </si>
+  <si>
+    <t>CIM68484</t>
+  </si>
+  <si>
+    <t>FEO KATJE</t>
+  </si>
+  <si>
+    <t>BAR NIGHT AND DAY DI OLIVA ANDREA</t>
+  </si>
+  <si>
+    <t>VIA ROMA 5</t>
+  </si>
+  <si>
+    <t>CIM69657</t>
+  </si>
+  <si>
+    <t>BAR STELLA R.S. DI SCHINELLO MIRIAM</t>
+  </si>
+  <si>
+    <t>BAR STELLA</t>
+  </si>
+  <si>
+    <t>VIA ZEFFIRO MASSA 313</t>
+  </si>
+  <si>
+    <t>CIM68497</t>
+  </si>
+  <si>
+    <t>PRYYMAK ANZHELA</t>
+  </si>
+  <si>
+    <t>BAR ANGY DI PRYYMAK ANZHELA</t>
+  </si>
+  <si>
+    <t>CIM69479</t>
+  </si>
+  <si>
+    <t>BAR DAL PICCHIO S.N.C. DI BORDA GIOVANNA  &amp; SALVATI MATTIA</t>
+  </si>
+  <si>
+    <t>BAR DAL PICCHIO</t>
+  </si>
+  <si>
+    <t>VIA CORSO MATUZIA 24</t>
+  </si>
+  <si>
+    <t>CSV69445</t>
+  </si>
+  <si>
+    <t>ALLUIGI SUSANNA</t>
+  </si>
+  <si>
+    <t>BAR HAITI</t>
+  </si>
+  <si>
+    <t>CORSO VITTORIO VENETO 226/R</t>
+  </si>
+  <si>
+    <t>CIM69672</t>
+  </si>
+  <si>
+    <t>ACRILIA SNC DI TRAVAGLINO GIULIA E BOERI  CRISTIAN</t>
+  </si>
+  <si>
+    <t>BAR DELLA POSTA</t>
+  </si>
+  <si>
+    <t>VIA SOLERI 5</t>
+  </si>
+  <si>
+    <t>CIM69893</t>
+  </si>
+  <si>
+    <t>MAG. GAMENET C/O FUNSEVEN TECNOLOGY SRLS</t>
+  </si>
+  <si>
+    <t>MAGAZZINO</t>
+  </si>
+  <si>
+    <t>VIA SAN FRANCESCO 350 A</t>
+  </si>
+  <si>
+    <t>ESATTORE</t>
+  </si>
+  <si>
+    <t>MATTEO</t>
+  </si>
+  <si>
+    <t>ALESSANDRO</t>
+  </si>
+  <si>
+    <t>LUCA</t>
+  </si>
+  <si>
+    <t>STEPHAN</t>
+  </si>
+  <si>
+    <t>MATTIA</t>
+  </si>
+  <si>
+    <t>DENOMIN. SEDE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -55,82 +1459,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -447,4 +1792,3443 @@
     </a:ext>
   </a:extLst>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J107"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.171875" customWidth="1"/>
+    <col min="2" max="2" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8359375" customWidth="1"/>
+    <col min="4" max="4" width="56.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.3671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2">
+        <v>49</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2">
+        <v>70</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2">
+        <v>189</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>456</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2">
+        <v>89</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2">
+        <v>94</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2">
+        <v>60</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>456</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2">
+        <v>105</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2">
+        <v>19</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2">
+        <v>60</v>
+      </c>
+      <c r="I12" s="2">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="2">
+        <v>135</v>
+      </c>
+      <c r="I13" s="2">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>457</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2">
+        <v>59</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>456</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2">
+        <v>75</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2">
+        <v>38</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>458</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2">
+        <v>185</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>456</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>3</v>
+      </c>
+      <c r="J19" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2">
+        <v>69</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>456</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2">
+        <v>35</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>460</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="2">
+        <v>59</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2">
+        <v>50</v>
+      </c>
+      <c r="I23" s="2">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2">
+        <v>52</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>456</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2">
+        <v>68</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>460</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="2">
+        <v>274</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3</v>
+      </c>
+      <c r="J26" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>459</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="2">
+        <v>90</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2">
+        <v>156</v>
+      </c>
+      <c r="I28" s="2">
+        <v>3</v>
+      </c>
+      <c r="J28" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>457</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="2">
+        <v>54</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>459</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="2">
+        <v>131</v>
+      </c>
+      <c r="I30" s="2">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>459</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="2">
+        <v>103</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>457</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="2">
+        <v>42</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>457</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="2">
+        <v>110</v>
+      </c>
+      <c r="I33" s="2">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="2">
+        <v>42</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>457</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2">
+        <v>57</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>456</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="2">
+        <v>130</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="2">
+        <v>96</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>457</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="2">
+        <v>82</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>460</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="2">
+        <v>82</v>
+      </c>
+      <c r="I39" s="2">
+        <v>2</v>
+      </c>
+      <c r="J39" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>460</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H40" s="2">
+        <v>67</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>456</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>457</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="2">
+        <v>85</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>457</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" s="2">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>458</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="2">
+        <v>31</v>
+      </c>
+      <c r="I44" s="2">
+        <v>2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>456</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="2">
+        <v>211</v>
+      </c>
+      <c r="I45" s="2">
+        <v>4</v>
+      </c>
+      <c r="J45" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>453</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="2">
+        <v>38</v>
+      </c>
+      <c r="I46" s="2">
+        <v>2</v>
+      </c>
+      <c r="J46" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>457</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="2">
+        <v>145</v>
+      </c>
+      <c r="I47" s="2">
+        <v>4</v>
+      </c>
+      <c r="J47" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>459</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="2">
+        <v>57</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1</v>
+      </c>
+      <c r="J48" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>456</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="2">
+        <v>70</v>
+      </c>
+      <c r="I49" s="2">
+        <v>3</v>
+      </c>
+      <c r="J49" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>458</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="2">
+        <v>87</v>
+      </c>
+      <c r="I50" s="2">
+        <v>2</v>
+      </c>
+      <c r="J50" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>458</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="2">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>457</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="2">
+        <v>35</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>459</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="2">
+        <v>163</v>
+      </c>
+      <c r="I53" s="2">
+        <v>2</v>
+      </c>
+      <c r="J53" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>459</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" s="2">
+        <v>45</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>459</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H55" s="2">
+        <v>46</v>
+      </c>
+      <c r="I55" s="2">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>453</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="2">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>458</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="2">
+        <v>44</v>
+      </c>
+      <c r="I57" s="2">
+        <v>4</v>
+      </c>
+      <c r="J57" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>459</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="2">
+        <v>25</v>
+      </c>
+      <c r="I58" s="2">
+        <v>2</v>
+      </c>
+      <c r="J58" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>459</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H59" s="2">
+        <v>64</v>
+      </c>
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
+      <c r="J59" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>460</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H60" s="2">
+        <v>49</v>
+      </c>
+      <c r="I60" s="2">
+        <v>3</v>
+      </c>
+      <c r="J60" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>460</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H61" s="2">
+        <v>40</v>
+      </c>
+      <c r="I61" s="2">
+        <v>2</v>
+      </c>
+      <c r="J61" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>460</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H62" s="2">
+        <v>32</v>
+      </c>
+      <c r="I62" s="2">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>458</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>460</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H64" s="2">
+        <v>94</v>
+      </c>
+      <c r="I64" s="2">
+        <v>2</v>
+      </c>
+      <c r="J64" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>459</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H65" s="2">
+        <v>50</v>
+      </c>
+      <c r="I65" s="2">
+        <v>3</v>
+      </c>
+      <c r="J65" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>457</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
+      <c r="J66" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>458</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" s="2">
+        <v>35</v>
+      </c>
+      <c r="I67" s="2">
+        <v>2</v>
+      </c>
+      <c r="J67" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>456</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="2">
+        <v>88</v>
+      </c>
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>456</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="2">
+        <v>49</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>459</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="2">
+        <v>110</v>
+      </c>
+      <c r="I70" s="2">
+        <v>2</v>
+      </c>
+      <c r="J70" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>459</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="2">
+        <v>160</v>
+      </c>
+      <c r="I71" s="2">
+        <v>2</v>
+      </c>
+      <c r="J71" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>456</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="2">
+        <v>70</v>
+      </c>
+      <c r="I72" s="2">
+        <v>1</v>
+      </c>
+      <c r="J72" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>459</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="2">
+        <v>35</v>
+      </c>
+      <c r="I73" s="2">
+        <v>1</v>
+      </c>
+      <c r="J73" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>459</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="2">
+        <v>74</v>
+      </c>
+      <c r="I74" s="2">
+        <v>2</v>
+      </c>
+      <c r="J74" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>457</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="2">
+        <v>40</v>
+      </c>
+      <c r="I75" s="2">
+        <v>3</v>
+      </c>
+      <c r="J75" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>456</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="2">
+        <v>60</v>
+      </c>
+      <c r="I76" s="2">
+        <v>1</v>
+      </c>
+      <c r="J76" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>456</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="2">
+        <v>70</v>
+      </c>
+      <c r="I77" s="2">
+        <v>2</v>
+      </c>
+      <c r="J77" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>457</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="2">
+        <v>45</v>
+      </c>
+      <c r="I78" s="2">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>456</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="2">
+        <v>101</v>
+      </c>
+      <c r="I79" s="2">
+        <v>2</v>
+      </c>
+      <c r="J79" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>460</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H80" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" s="2">
+        <v>1</v>
+      </c>
+      <c r="J80" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>460</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H81" s="2">
+        <v>98</v>
+      </c>
+      <c r="I81" s="2">
+        <v>3</v>
+      </c>
+      <c r="J81" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>456</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="2">
+        <v>60</v>
+      </c>
+      <c r="I82" s="2">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>456</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="2">
+        <v>80</v>
+      </c>
+      <c r="I83" s="2">
+        <v>1</v>
+      </c>
+      <c r="J83" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>457</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="2">
+        <v>38</v>
+      </c>
+      <c r="I84" s="2">
+        <v>2</v>
+      </c>
+      <c r="J84" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>456</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="2">
+        <v>45</v>
+      </c>
+      <c r="I85" s="2">
+        <v>1</v>
+      </c>
+      <c r="J85" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>458</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" s="2">
+        <v>40</v>
+      </c>
+      <c r="I86" s="2">
+        <v>2</v>
+      </c>
+      <c r="J86" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>456</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="2">
+        <v>35</v>
+      </c>
+      <c r="I87" s="2">
+        <v>1</v>
+      </c>
+      <c r="J87" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>456</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="2">
+        <v>60</v>
+      </c>
+      <c r="I88" s="2">
+        <v>1</v>
+      </c>
+      <c r="J88" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>460</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H89" s="2">
+        <v>55</v>
+      </c>
+      <c r="I89" s="2">
+        <v>3</v>
+      </c>
+      <c r="J89" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>458</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="2">
+        <v>64</v>
+      </c>
+      <c r="I90" s="2">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>453</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="2">
+        <v>35</v>
+      </c>
+      <c r="I91" s="2">
+        <v>2</v>
+      </c>
+      <c r="J91" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>456</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" s="2">
+        <v>50</v>
+      </c>
+      <c r="I92" s="2">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>458</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="2">
+        <v>52</v>
+      </c>
+      <c r="I93" s="2">
+        <v>1</v>
+      </c>
+      <c r="J93" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>457</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" s="2">
+        <v>55</v>
+      </c>
+      <c r="I94" s="2">
+        <v>1</v>
+      </c>
+      <c r="J94" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>457</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="2">
+        <v>47</v>
+      </c>
+      <c r="I95" s="2">
+        <v>2</v>
+      </c>
+      <c r="J95" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>457</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" s="2">
+        <v>2</v>
+      </c>
+      <c r="J96" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>457</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="2">
+        <v>40</v>
+      </c>
+      <c r="I97" s="2">
+        <v>2</v>
+      </c>
+      <c r="J97" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>453</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="2">
+        <v>130</v>
+      </c>
+      <c r="I98" s="2">
+        <v>2</v>
+      </c>
+      <c r="J98" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>456</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" s="2">
+        <v>55</v>
+      </c>
+      <c r="I99" s="2">
+        <v>2</v>
+      </c>
+      <c r="J99" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>456</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" s="2">
+        <v>50</v>
+      </c>
+      <c r="I100" s="2">
+        <v>1</v>
+      </c>
+      <c r="J100" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>456</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" s="2">
+        <v>50</v>
+      </c>
+      <c r="I101" s="2">
+        <v>2</v>
+      </c>
+      <c r="J101" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>458</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" s="2">
+        <v>2</v>
+      </c>
+      <c r="J102" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>453</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H103" s="2">
+        <v>32</v>
+      </c>
+      <c r="I103" s="2">
+        <v>2</v>
+      </c>
+      <c r="J103" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>458</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H104" s="2">
+        <v>42</v>
+      </c>
+      <c r="I104" s="2">
+        <v>2</v>
+      </c>
+      <c r="J104" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>460</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H105" s="2">
+        <v>100</v>
+      </c>
+      <c r="I105" s="2">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>457</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" s="2">
+        <v>65</v>
+      </c>
+      <c r="I106" s="2">
+        <v>1</v>
+      </c>
+      <c r="J106" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>453</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2">
+        <v>24</v>
+      </c>
+      <c r="J107" s="2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>